--- a/results/Int Task Remove ACC -0.0/Rando_5_permute.xlsx
+++ b/results/Int Task Remove ACC -0.0/Rando_5_permute.xlsx
@@ -440,87 +440,87 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6138827484966427</v>
+        <v>0.599373424662719</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6150238401417342</v>
+        <v>0.599373424662719</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6143921282023785</v>
+        <v>0.608014856495053</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6182231772497191</v>
+        <v>0.6096653278458803</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6187021428642234</v>
+        <v>0.6057015832449447</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.61874292027543</v>
+        <v>0.6031844229388033</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6177953523663966</v>
+        <v>0.5953495277480145</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6183765994432644</v>
+        <v>0.5789664706046682</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.619915101880447</v>
+        <v>0.5772240811114526</v>
       </c>
     </row>
     <row r="11">
@@ -530,737 +530,737 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6273435746965574</v>
+        <v>0.5788648650109987</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6262736745539041</v>
+        <v>0.5826046717846448</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.630584365084443</v>
+        <v>0.5463427393228517</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.627638704026285</v>
+        <v>0.5422255725283708</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6135572050756838</v>
+        <v>0.5633180827317351</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5967961120428086</v>
+        <v>0.5643472054631818</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5884822512375156</v>
+        <v>0.5803037894605937</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5991805767953551</v>
+        <v>0.6186192363044221</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5368657084951288</v>
+        <v>0.6200554572792409</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5340941962704664</v>
+        <v>0.6183130677860253</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.50291637341475</v>
+        <v>0.615408860007768</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5052490215674206</v>
+        <v>0.615408860007768</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5042606762471805</v>
+        <v>0.6073603903096649</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.49048602168367</v>
+        <v>0.6058626652836892</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.488917105155256</v>
+        <v>0.6053021448467716</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4863902573978334</v>
+        <v>0.5984956965187356</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4433626540192109</v>
+        <v>0.5920154674803525</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4443005344769633</v>
+        <v>0.5619302990133218</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4532771971815375</v>
+        <v>0.5458450746744792</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.456650007254324</v>
+        <v>0.5635233215251563</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.463323760028765</v>
+        <v>0.5462535246552394</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.463323760028765</v>
+        <v>0.6205094157520661</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.490354001998769</v>
+        <v>0.5855890826479274</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.490354001998769</v>
+        <v>0.5883295049126642</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.490354001998769</v>
+        <v>0.5340390003271205</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4892944651760909</v>
+        <v>0.5909041140577985</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5530131127538225</v>
+        <v>0.5759863402431145</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5412241604133794</v>
+        <v>0.5751306904764694</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5451969165969019</v>
+        <v>0.5866957049896231</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5588803288867181</v>
+        <v>0.5410175698825701</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5597159278821069</v>
+        <v>0.5410175698825701</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.512408723932871</v>
+        <v>0.5233296355806117</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4932009862275983</v>
+        <v>0.5234416044942565</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4961543071309554</v>
+        <v>0.5259069482005221</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5023691450621484</v>
+        <v>0.5207329480581392</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5023691450621484</v>
+        <v>0.5159633426843522</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5027257784430328</v>
+        <v>0.5020449533785775</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5269637815484242</v>
+        <v>0.4999051530932708</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.524211644226324</v>
+        <v>0.4731644082138773</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.524211644226324</v>
+        <v>0.4477037586409812</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5264122726940937</v>
+        <v>0.443628045126401</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5285009322482186</v>
+        <v>0.4460927129639726</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5447630088953331</v>
+        <v>0.4460927129639726</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5441312969559775</v>
+        <v>0.4564751825521343</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5527416388283861</v>
+        <v>0.4663399367206671</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5527416388283861</v>
+        <v>0.4514953820145032</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5465261250284992</v>
+        <v>0.4652326385102773</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5384251628618263</v>
+        <v>0.470465439229041</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.531007729234385</v>
+        <v>0.4911294486803889</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5422161103666543</v>
+        <v>0.4971714895154743</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5203695559903143</v>
+        <v>0.4843941918547909</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5203695559903143</v>
+        <v>0.4881236353084619</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5416355391584804</v>
+        <v>0.4864019724551967</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5244252187336383</v>
+        <v>0.4653820054916584</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5261268308156474</v>
+        <v>0.4368339877244222</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5240996753126794</v>
+        <v>0.4306184739245352</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5212770223568353</v>
+        <v>0.4306184739245352</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5271061645533004</v>
+        <v>0.4355919663543553</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5250375557704318</v>
+        <v>0.4468514882178063</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5200343251180742</v>
+        <v>0.449052116685576</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5389980742248012</v>
+        <v>0.4502567399879065</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5536705077035514</v>
+        <v>0.4379480446217523</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5568705206802304</v>
+        <v>0.4375506338296613</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5488096600560701</v>
+        <v>0.4092375930783836</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5350329778864775</v>
+        <v>0.4163999989186101</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5406084440331158</v>
+        <v>0.4163999989186101</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5112324871156898</v>
+        <v>0.4163999989186101</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5056680601577207</v>
+        <v>0.4163999989186101</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5167541090563702</v>
+        <v>0.3955253437242888</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5233172446545545</v>
+        <v>0.4279602823509057</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5246725866756542</v>
+        <v>0.3661687617094251</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5052091453144727</v>
+        <v>0.4895343985624723</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5107348224673173</v>
+        <v>0.4905738846138942</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5117542577474828</v>
+        <v>0.505083208447818</v>
       </c>
     </row>
     <row r="85">
@@ -1270,57 +1270,57 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5096144574621762</v>
+        <v>0.5063466323265293</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4931906229076232</v>
+        <v>0.4097679247136344</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4989057685843615</v>
+        <v>0.4475559686865528</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4989057685843615</v>
+        <v>0.4827881025482052</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4964908897405836</v>
+        <v>0.4907439782352258</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4951873643193597</v>
+        <v>0.4963575183182946</v>
       </c>
     </row>
   </sheetData>
